--- a/12HBosaro_manager.xlsx
+++ b/12HBosaro_manager.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Moretto\Documents\12ore26\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9271CF70-0945-4B48-B2D3-D51037ED388C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F436FC19-B087-4523-A05F-CF35B1097C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/12HBosaro_manager.xlsx
+++ b/12HBosaro_manager.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Moretto\Documents\12ore26\12orebosaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F436FC19-B087-4523-A05F-CF35B1097C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF6F842-799A-4D56-A289-69DE97427695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2119" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="659">
   <si>
     <t>12 ORE BOSARO 2026 — Tournament Manager</t>
   </si>
@@ -1643,9 +1643,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>14:15</t>
-  </si>
-  <si>
     <t>M02</t>
   </si>
   <si>
@@ -1661,9 +1658,6 @@
     <t>M04</t>
   </si>
   <si>
-    <t>14:45</t>
-  </si>
-  <si>
     <t>M05</t>
   </si>
   <si>
@@ -1673,9 +1667,6 @@
     <t>M07</t>
   </si>
   <si>
-    <t>15:15</t>
-  </si>
-  <si>
     <t>M08</t>
   </si>
   <si>
@@ -1685,9 +1676,6 @@
     <t>M10</t>
   </si>
   <si>
-    <t>15:45</t>
-  </si>
-  <si>
     <t>M11</t>
   </si>
   <si>
@@ -1697,9 +1685,6 @@
     <t>M13</t>
   </si>
   <si>
-    <t>16:30</t>
-  </si>
-  <si>
     <t>M14</t>
   </si>
   <si>
@@ -1709,9 +1694,6 @@
     <t>M16</t>
   </si>
   <si>
-    <t>17:00</t>
-  </si>
-  <si>
     <t>M17</t>
   </si>
   <si>
@@ -1721,9 +1703,6 @@
     <t>M19</t>
   </si>
   <si>
-    <t>17:30</t>
-  </si>
-  <si>
     <t>M20</t>
   </si>
   <si>
@@ -1731,9 +1710,6 @@
   </si>
   <si>
     <t>M22</t>
-  </si>
-  <si>
-    <t>18:00</t>
   </si>
   <si>
     <t>M23</t>
@@ -2052,6 +2028,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="167" formatCode="h:mm;@"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2127,7 +2107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2155,6 +2135,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2496,37 +2484,37 @@
         <v>30</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>581</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>575</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>577</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>574</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>588</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>589</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>590</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>591</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>592</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>583</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>584</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>585</v>
       </c>
       <c r="M1" s="4"/>
       <c r="N1" s="4"/>
@@ -3176,23 +3164,23 @@
       </c>
       <c r="C15" t="str">
         <f>INDEX(StandingsData!$B$14:$B$17,MATCH(LARGE(StandingsData!$M$14:$M$17,2),StandingsData!$M$14:$M$17,0))</f>
-        <v>Boldò Glimt</v>
+        <v>All Blacks</v>
       </c>
       <c r="D15">
         <f>INDEX(StandingsData!$K$14:$K$17,MATCH(LARGE(StandingsData!$M$14:$M$17,2),StandingsData!$M$14:$M$17,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15">
         <f>INDEX(StandingsData!$C$14:$C$17,MATCH(LARGE(StandingsData!$M$14:$M$17,2),StandingsData!$M$14:$M$17,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15">
         <f>INDEX(StandingsData!$D$14:$D$17,MATCH(LARGE(StandingsData!$M$14:$M$17,2),StandingsData!$M$14:$M$17,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15">
         <f>INDEX(StandingsData!$E$14:$E$17,MATCH(LARGE(StandingsData!$M$14:$M$17,2),StandingsData!$M$14:$M$17,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15">
         <f>INDEX(StandingsData!$F$14:$F$17,MATCH(LARGE(StandingsData!$M$14:$M$17,2),StandingsData!$M$14:$M$17,0))</f>
@@ -3200,19 +3188,19 @@
       </c>
       <c r="I15">
         <f>INDEX(StandingsData!$G$14:$G$17,MATCH(LARGE(StandingsData!$M$14:$M$17,2),StandingsData!$M$14:$M$17,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <f>INDEX(StandingsData!$H$14:$H$17,MATCH(LARGE(StandingsData!$M$14:$M$17,2),StandingsData!$M$14:$M$17,0))</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <f>INDEX(StandingsData!$I$14:$I$17,MATCH(LARGE(StandingsData!$M$14:$M$17,2),StandingsData!$M$14:$M$17,0))</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L15">
         <f>INDEX(StandingsData!$J$14:$J$17,MATCH(LARGE(StandingsData!$M$14:$M$17,2),StandingsData!$M$14:$M$17,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.3">
@@ -3224,15 +3212,15 @@
       </c>
       <c r="C16" t="str">
         <f>INDEX(StandingsData!$B$14:$B$17,MATCH(LARGE(StandingsData!$M$14:$M$17,3),StandingsData!$M$14:$M$17,0))</f>
-        <v>All Blacks</v>
+        <v>Boldò Glimt</v>
       </c>
       <c r="D16">
         <f>INDEX(StandingsData!$K$14:$K$17,MATCH(LARGE(StandingsData!$M$14:$M$17,3),StandingsData!$M$14:$M$17,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <f>INDEX(StandingsData!$C$14:$C$17,MATCH(LARGE(StandingsData!$M$14:$M$17,3),StandingsData!$M$14:$M$17,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16">
         <f>INDEX(StandingsData!$D$14:$D$17,MATCH(LARGE(StandingsData!$M$14:$M$17,3),StandingsData!$M$14:$M$17,0))</f>
@@ -3244,7 +3232,7 @@
       </c>
       <c r="H16">
         <f>INDEX(StandingsData!$F$14:$F$17,MATCH(LARGE(StandingsData!$M$14:$M$17,3),StandingsData!$M$14:$M$17,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16">
         <f>INDEX(StandingsData!$G$14:$G$17,MATCH(LARGE(StandingsData!$M$14:$M$17,3),StandingsData!$M$14:$M$17,0))</f>
@@ -3252,15 +3240,15 @@
       </c>
       <c r="J16">
         <f>INDEX(StandingsData!$H$14:$H$17,MATCH(LARGE(StandingsData!$M$14:$M$17,3),StandingsData!$M$14:$M$17,0))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K16">
         <f>INDEX(StandingsData!$I$14:$I$17,MATCH(LARGE(StandingsData!$M$14:$M$17,3),StandingsData!$M$14:$M$17,0))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L16">
         <f>INDEX(StandingsData!$J$14:$J$17,MATCH(LARGE(StandingsData!$M$14:$M$17,3),StandingsData!$M$14:$M$17,0))</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
@@ -3382,16 +3370,16 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="B2" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="E2" t="s">
         <v>531</v>
       </c>
       <c r="F2" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -3407,16 +3395,16 @@
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="B3" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="E3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F3" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -3432,16 +3420,16 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="B4" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="E4" t="s">
         <v>531</v>
       </c>
       <c r="F4" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -3457,16 +3445,16 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="B5" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="E5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F5" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -3482,16 +3470,16 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="B6" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="E6" t="s">
         <v>531</v>
       </c>
       <c r="F6" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -3507,16 +3495,16 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="B7" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="E7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F7" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -3532,13 +3520,13 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="B8" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="F8" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -3570,7 +3558,7 @@
         <v>31</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>35</v>
@@ -3634,7 +3622,7 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="C2" t="s">
         <v>77</v>
@@ -3690,7 +3678,7 @@
         <v>37</v>
       </c>
       <c r="B3" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="C3" t="s">
         <v>80</v>
@@ -3746,7 +3734,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="C4" t="s">
         <v>83</v>
@@ -3802,7 +3790,7 @@
         <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="C5" t="s">
         <v>86</v>
@@ -3858,7 +3846,7 @@
         <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="C6" t="s">
         <v>89</v>
@@ -3914,7 +3902,7 @@
         <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="C7" t="s">
         <v>92</v>
@@ -3970,7 +3958,7 @@
         <v>48</v>
       </c>
       <c r="B8" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="C8" t="s">
         <v>95</v>
@@ -4023,7 +4011,7 @@
         <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="C9" t="s">
         <v>99</v>
@@ -4076,7 +4064,7 @@
         <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="C10" t="s">
         <v>102</v>
@@ -4126,7 +4114,7 @@
         <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="C11" t="s">
         <v>105</v>
@@ -4170,7 +4158,7 @@
         <v>57</v>
       </c>
       <c r="B12" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="E12" t="s">
         <v>149</v>
@@ -4190,7 +4178,7 @@
         <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="E13" t="s">
         <v>151</v>
@@ -4201,7 +4189,7 @@
         <v>62</v>
       </c>
       <c r="B14" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.3">
@@ -4209,7 +4197,7 @@
         <v>64</v>
       </c>
       <c r="B15" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.3">
@@ -4217,7 +4205,7 @@
         <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -4225,7 +4213,7 @@
         <v>68</v>
       </c>
       <c r="B17" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -4252,7 +4240,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="72" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -4310,7 +4298,7 @@
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -4325,7 +4313,7 @@
       <c r="L3" s="9"/>
       <c r="M3" s="1"/>
       <c r="N3" s="8" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
@@ -4342,53 +4330,53 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
+        <v>620</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>623</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>628</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>629</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="K4" s="7" t="s">
         <v>630</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="L4" s="7" t="s">
         <v>631</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>632</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>633</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>634</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>635</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>636</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>637</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>638</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>639</v>
       </c>
       <c r="M4" s="1"/>
       <c r="N4" s="7" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
@@ -4400,7 +4388,7 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="str">
         <f>Standings!A2</f>
         <v>A</v>
@@ -4476,7 +4464,7 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="str">
         <f>Standings!A3</f>
         <v>A</v>
@@ -4552,7 +4540,7 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="str">
         <f>Standings!A4</f>
         <v>A</v>
@@ -4628,7 +4616,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="str">
         <f>Standings!A5</f>
         <v>A</v>
@@ -4684,11 +4672,11 @@
       </c>
       <c r="O8" s="1" t="str">
         <f>IF(TopScorers!B5="","",TopScorers!B5)</f>
-        <v>LUCA CAVALLARO</v>
+        <v>DAVIDE GIRARDELLO</v>
       </c>
       <c r="P8" s="1" t="str">
         <f>IF(TopScorers!C5="","",TopScorers!C5)</f>
-        <v>Coca Juniors</v>
+        <v>All Blacks</v>
       </c>
       <c r="Q8" s="1">
         <f>IF(TopScorers!D5="","",TopScorers!D5)</f>
@@ -4760,11 +4748,11 @@
       </c>
       <c r="O9" s="1" t="str">
         <f>IF(TopScorers!B6="","",TopScorers!B6)</f>
-        <v>KEVIN DOBROZI</v>
+        <v>ANGELO REDI</v>
       </c>
       <c r="P9" s="1" t="str">
         <f>IF(TopScorers!C6="","",TopScorers!C6)</f>
-        <v>Coca Juniors</v>
+        <v>Boldò Glimt</v>
       </c>
       <c r="Q9" s="1">
         <f>IF(TopScorers!D6="","",TopScorers!D6)</f>
@@ -4836,7 +4824,7 @@
       </c>
       <c r="O10" s="1" t="str">
         <f>IF(TopScorers!B7="","",TopScorers!B7)</f>
-        <v>TOMMASO PAVAN</v>
+        <v>LUCA CAVALLARO</v>
       </c>
       <c r="P10" s="1" t="str">
         <f>IF(TopScorers!C7="","",TopScorers!C7)</f>
@@ -4856,7 +4844,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="str">
         <f>Standings!A8</f>
         <v>B</v>
@@ -4912,7 +4900,7 @@
       </c>
       <c r="O11" s="1" t="str">
         <f>IF(TopScorers!B8="","",TopScorers!B8)</f>
-        <v>GIAN MARCO MARANGONI</v>
+        <v>KEVIN DOBROZI</v>
       </c>
       <c r="P11" s="1" t="str">
         <f>IF(TopScorers!C8="","",TopScorers!C8)</f>
@@ -4988,15 +4976,15 @@
       </c>
       <c r="O12" s="1" t="str">
         <f>IF(TopScorers!B9="","",TopScorers!B9)</f>
-        <v>GIOVANNI BALLO</v>
+        <v>TOMMASO PAVAN</v>
       </c>
       <c r="P12" s="1" t="str">
         <f>IF(TopScorers!C9="","",TopScorers!C9)</f>
-        <v>Fatine FC</v>
+        <v>Coca Juniors</v>
       </c>
       <c r="Q12" s="1">
         <f>IF(TopScorers!D9="","",TopScorers!D9)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
@@ -5064,15 +5052,15 @@
       </c>
       <c r="O13" s="1" t="str">
         <f>IF(TopScorers!B10="","",TopScorers!B10)</f>
-        <v>DANIELE MARZOLLA</v>
+        <v>GIAN MARCO MARANGONI</v>
       </c>
       <c r="P13" s="1" t="str">
         <f>IF(TopScorers!C10="","",TopScorers!C10)</f>
-        <v>Fatine FC</v>
+        <v>Coca Juniors</v>
       </c>
       <c r="Q13" s="1">
         <f>IF(TopScorers!D10="","",TopScorers!D10)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
@@ -5140,7 +5128,7 @@
       </c>
       <c r="O14" s="1" t="str">
         <f>IF(TopScorers!B11="","",TopScorers!B11)</f>
-        <v>NICHOLAS MILAN</v>
+        <v>GIOVANNI BALLO</v>
       </c>
       <c r="P14" s="1" t="str">
         <f>IF(TopScorers!C11="","",TopScorers!C11)</f>
@@ -5216,7 +5204,7 @@
       </c>
       <c r="O15" s="1" t="str">
         <f>IF(TopScorers!B12="","",TopScorers!B12)</f>
-        <v>ALESSIO MILAN</v>
+        <v>DANIELE MARZOLLA</v>
       </c>
       <c r="P15" s="1" t="str">
         <f>IF(TopScorers!C12="","",TopScorers!C12)</f>
@@ -5292,7 +5280,7 @@
       </c>
       <c r="O16" s="1" t="str">
         <f>IF(TopScorers!B13="","",TopScorers!B13)</f>
-        <v>NICOLA MARINI</v>
+        <v>NICHOLAS MILAN</v>
       </c>
       <c r="P16" s="1" t="str">
         <f>IF(TopScorers!C13="","",TopScorers!C13)</f>
@@ -5368,7 +5356,7 @@
       </c>
       <c r="O17" s="1" t="str">
         <f>IF(TopScorers!B14="","",TopScorers!B14)</f>
-        <v>LUCA ROSSETTO</v>
+        <v>ALESSIO MILAN</v>
       </c>
       <c r="P17" s="1" t="str">
         <f>IF(TopScorers!C14="","",TopScorers!C14)</f>
@@ -5399,23 +5387,23 @@
       </c>
       <c r="C18" s="1" t="str">
         <f>Standings!C15</f>
-        <v>Boldò Glimt</v>
+        <v>All Blacks</v>
       </c>
       <c r="D18" s="1">
         <f>Standings!D15</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="1">
         <f>Standings!E15</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="1">
         <f>Standings!F15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
         <f>Standings!G15</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" s="1">
         <f>Standings!H15</f>
@@ -5423,19 +5411,19 @@
       </c>
       <c r="I18" s="1">
         <f>Standings!I15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="1">
         <f>Standings!J15</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K18" s="1">
         <f>Standings!K15</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L18" s="1">
         <f>Standings!L15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="1"/>
       <c r="N18" s="1">
@@ -5444,11 +5432,11 @@
       </c>
       <c r="O18" s="1" t="str">
         <f>IF(TopScorers!B15="","",TopScorers!B15)</f>
-        <v>LUCA BACCO</v>
+        <v>NICOLA MARINI</v>
       </c>
       <c r="P18" s="1" t="str">
         <f>IF(TopScorers!C15="","",TopScorers!C15)</f>
-        <v>Moviola Utd</v>
+        <v>Fatine FC</v>
       </c>
       <c r="Q18" s="1">
         <f>IF(TopScorers!D15="","",TopScorers!D15)</f>
@@ -5475,15 +5463,15 @@
       </c>
       <c r="C19" s="1" t="str">
         <f>Standings!C16</f>
-        <v>All Blacks</v>
+        <v>Boldò Glimt</v>
       </c>
       <c r="D19" s="1">
         <f>Standings!D16</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="1">
         <f>Standings!E16</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="1">
         <f>Standings!F16</f>
@@ -5495,7 +5483,7 @@
       </c>
       <c r="H19" s="1">
         <f>Standings!H16</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" s="1">
         <f>Standings!I16</f>
@@ -5503,15 +5491,15 @@
       </c>
       <c r="J19" s="1">
         <f>Standings!J16</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K19" s="1">
         <f>Standings!K16</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L19" s="1">
         <f>Standings!L16</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="M19" s="1"/>
       <c r="N19" s="1">
@@ -5520,11 +5508,11 @@
       </c>
       <c r="O19" s="1" t="str">
         <f>IF(TopScorers!B16="","",TopScorers!B16)</f>
-        <v>FILIPPO SCARANELLO</v>
+        <v>LUCA ROSSETTO</v>
       </c>
       <c r="P19" s="1" t="str">
         <f>IF(TopScorers!C16="","",TopScorers!C16)</f>
-        <v>Moviola Utd</v>
+        <v>Fatine FC</v>
       </c>
       <c r="Q19" s="1">
         <f>IF(TopScorers!D16="","",TopScorers!D16)</f>
@@ -5540,7 +5528,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="str">
         <f>Standings!A17</f>
         <v>D</v>
@@ -5596,11 +5584,11 @@
       </c>
       <c r="O20" s="1" t="str">
         <f>IF(TopScorers!B17="","",TopScorers!B17)</f>
-        <v>GIANLUCA PAVAN</v>
+        <v>LUCA BACCO</v>
       </c>
       <c r="P20" s="1" t="str">
         <f>IF(TopScorers!C17="","",TopScorers!C17)</f>
-        <v>Astolfi Impianti Elettrici</v>
+        <v>Moviola Utd</v>
       </c>
       <c r="Q20" s="1">
         <f>IF(TopScorers!D17="","",TopScorers!D17)</f>
@@ -5636,11 +5624,11 @@
       </c>
       <c r="O21" s="1" t="str">
         <f>IF(TopScorers!B18="","",TopScorers!B18)</f>
-        <v>ELIA NAGLIERI</v>
+        <v>FILIPPO SCARANELLO</v>
       </c>
       <c r="P21" s="1" t="str">
         <f>IF(TopScorers!C18="","",TopScorers!C18)</f>
-        <v>Astolfi Impianti Elettrici</v>
+        <v>Moviola Utd</v>
       </c>
       <c r="Q21" s="1">
         <f>IF(TopScorers!D18="","",TopScorers!D18)</f>
@@ -5656,7 +5644,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -5676,7 +5664,7 @@
       </c>
       <c r="O22" s="5" t="str">
         <f>IF(TopScorers!B19="","",TopScorers!B19)</f>
-        <v>FILIPPO ZANINI</v>
+        <v>GIANLUCA PAVAN</v>
       </c>
       <c r="P22" s="5" t="str">
         <f>IF(TopScorers!C19="","",TopScorers!C19)</f>
@@ -5698,7 +5686,7 @@
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -5718,11 +5706,11 @@
       </c>
       <c r="O23" s="10" t="str">
         <f>IF(TopScorers!B20="","",TopScorers!B20)</f>
-        <v>DANIEL TARGA</v>
+        <v>ELIA NAGLIERI</v>
       </c>
       <c r="P23" s="10" t="str">
         <f>IF(TopScorers!C20="","",TopScorers!C20)</f>
-        <v>Totani</v>
+        <v>Astolfi Impianti Elettrici</v>
       </c>
       <c r="Q23" s="10">
         <f>IF(TopScorers!D20="","",TopScorers!D20)</f>
@@ -5740,61 +5728,61 @@
     </row>
     <row r="24" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
+        <v>635</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>636</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>620</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>638</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>639</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>641</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="J24" s="7" t="s">
         <v>643</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="K24" s="7" t="s">
         <v>644</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>628</v>
-      </c>
-      <c r="D24" s="7" t="s">
+      <c r="L24" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="M24" s="7" t="s">
         <v>646</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="N24" s="7" t="s">
         <v>647</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="O24" s="7" t="s">
         <v>648</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="P24" s="7" t="s">
         <v>649</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="Q24" s="7" t="s">
         <v>650</v>
       </c>
-      <c r="J24" s="7" t="s">
+      <c r="R24" s="7" t="s">
         <v>651</v>
       </c>
-      <c r="K24" s="7" t="s">
+      <c r="S24" s="7" t="s">
         <v>652</v>
-      </c>
-      <c r="L24" s="7" t="s">
-        <v>653</v>
-      </c>
-      <c r="M24" s="7" t="s">
-        <v>654</v>
-      </c>
-      <c r="N24" s="7" t="s">
-        <v>655</v>
-      </c>
-      <c r="O24" s="7" t="s">
-        <v>656</v>
-      </c>
-      <c r="P24" s="7" t="s">
-        <v>657</v>
-      </c>
-      <c r="Q24" s="7" t="s">
-        <v>658</v>
-      </c>
-      <c r="R24" s="7" t="s">
-        <v>659</v>
-      </c>
-      <c r="S24" s="7" t="s">
-        <v>660</v>
       </c>
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
@@ -5804,7 +5792,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="str">
         <f>Matches!A2</f>
         <v>M01</v>
@@ -5825,9 +5813,9 @@
         <f>Matches!E2</f>
         <v>1</v>
       </c>
-      <c r="F25" s="1" t="str">
+      <c r="F25" s="14">
         <f>Matches!F2</f>
-        <v>14:15</v>
+        <v>0.69861111111111107</v>
       </c>
       <c r="G25" s="1" t="str">
         <f>Matches!G2</f>
@@ -5839,15 +5827,15 @@
       </c>
       <c r="I25" s="1">
         <f>IF(Matches!I2="","",Matches!I2)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J25" s="1">
         <f>IF(Matches!J2="","",Matches!J2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" s="1" t="str">
         <f>IF(Matches!K2="","",Matches!K2)</f>
-        <v>Boldò Glimt</v>
+        <v/>
       </c>
       <c r="L25" s="1" t="str">
         <f>Matches!L2</f>
@@ -5855,19 +5843,19 @@
       </c>
       <c r="M25" s="1">
         <f>IF(Matches!M2="","",Matches!M2)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N25" s="1">
         <f>IF(Matches!N2="","",Matches!N2)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O25" s="1" t="str">
         <f>IF(Matches!O2="","",Matches!O2)</f>
-        <v>Boldò Glimt</v>
+        <v>All Blacks</v>
       </c>
       <c r="P25" s="1" t="str">
         <f>IF(Matches!P2="","",Matches!P2)</f>
-        <v>All Blacks 1 - 1 Boldò Glimt (rigori: Boldò Glimt)</v>
+        <v>All Blacks 4 - 2 Boldò Glimt</v>
       </c>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
@@ -5901,9 +5889,9 @@
         <f>Matches!E3</f>
         <v>2</v>
       </c>
-      <c r="F26" s="1" t="str">
+      <c r="F26" s="14">
         <f>Matches!F3</f>
-        <v>14:15</v>
+        <v>0.59375</v>
       </c>
       <c r="G26" s="1" t="str">
         <f>Matches!G3</f>
@@ -5977,9 +5965,9 @@
         <f>Matches!E4</f>
         <v>3 (S)</v>
       </c>
-      <c r="F27" s="1" t="str">
+      <c r="F27" s="14">
         <f>Matches!F4</f>
-        <v>14:15</v>
+        <v>0.59375</v>
       </c>
       <c r="G27" s="1" t="str">
         <f>Matches!G4</f>
@@ -6032,7 +6020,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="str">
         <f>Matches!A5</f>
         <v>M04</v>
@@ -6053,9 +6041,9 @@
         <f>Matches!E5</f>
         <v>1</v>
       </c>
-      <c r="F28" s="1" t="str">
+      <c r="F28" s="14">
         <f>Matches!F5</f>
-        <v>14:45</v>
+        <v>0.61458333333333337</v>
       </c>
       <c r="G28" s="1" t="str">
         <f>Matches!G5</f>
@@ -6108,7 +6096,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="str">
         <f>Matches!A6</f>
         <v>M05</v>
@@ -6129,9 +6117,9 @@
         <f>Matches!E6</f>
         <v>2</v>
       </c>
-      <c r="F29" s="1" t="str">
+      <c r="F29" s="14">
         <f>Matches!F6</f>
-        <v>14:45</v>
+        <v>0.61458333333333337</v>
       </c>
       <c r="G29" s="1" t="str">
         <f>Matches!G6</f>
@@ -6184,7 +6172,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="str">
         <f>Matches!A7</f>
         <v>M06</v>
@@ -6205,9 +6193,9 @@
         <f>Matches!E7</f>
         <v>3 (S)</v>
       </c>
-      <c r="F30" s="1" t="str">
+      <c r="F30" s="14">
         <f>Matches!F7</f>
-        <v>14:45</v>
+        <v>0.61458333333333337</v>
       </c>
       <c r="G30" s="1" t="str">
         <f>Matches!G7</f>
@@ -6260,7 +6248,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="str">
         <f>Matches!A8</f>
         <v>M07</v>
@@ -6281,9 +6269,9 @@
         <f>Matches!E8</f>
         <v>1</v>
       </c>
-      <c r="F31" s="1" t="str">
+      <c r="F31" s="14">
         <f>Matches!F8</f>
-        <v>15:15</v>
+        <v>0.63541666666666663</v>
       </c>
       <c r="G31" s="1" t="str">
         <f>Matches!G8</f>
@@ -6336,7 +6324,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="str">
         <f>Matches!A9</f>
         <v>M08</v>
@@ -6357,9 +6345,9 @@
         <f>Matches!E9</f>
         <v>2</v>
       </c>
-      <c r="F32" s="1" t="str">
+      <c r="F32" s="14">
         <f>Matches!F9</f>
-        <v>15:15</v>
+        <v>0.63541666666666663</v>
       </c>
       <c r="G32" s="1" t="str">
         <f>Matches!G9</f>
@@ -6412,7 +6400,7 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="str">
         <f>Matches!A10</f>
         <v>M09</v>
@@ -6433,9 +6421,9 @@
         <f>Matches!E10</f>
         <v>3 (S)</v>
       </c>
-      <c r="F33" s="1" t="str">
+      <c r="F33" s="14">
         <f>Matches!F10</f>
-        <v>15:15</v>
+        <v>0.63541666666666663</v>
       </c>
       <c r="G33" s="1" t="str">
         <f>Matches!G10</f>
@@ -6488,7 +6476,7 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="str">
         <f>Matches!A11</f>
         <v>M10</v>
@@ -6509,9 +6497,9 @@
         <f>Matches!E11</f>
         <v>1</v>
       </c>
-      <c r="F34" s="1" t="str">
+      <c r="F34" s="14">
         <f>Matches!F11</f>
-        <v>15:45</v>
+        <v>0.65625</v>
       </c>
       <c r="G34" s="1" t="str">
         <f>Matches!G11</f>
@@ -6585,9 +6573,9 @@
         <f>Matches!E12</f>
         <v>2</v>
       </c>
-      <c r="F35" s="1" t="str">
+      <c r="F35" s="14">
         <f>Matches!F12</f>
-        <v>15:45</v>
+        <v>0.65625</v>
       </c>
       <c r="G35" s="1" t="str">
         <f>Matches!G12</f>
@@ -6661,9 +6649,9 @@
         <f>Matches!E13</f>
         <v>3 (S)</v>
       </c>
-      <c r="F36" s="1" t="str">
+      <c r="F36" s="14">
         <f>Matches!F13</f>
-        <v>15:45</v>
+        <v>0.65625</v>
       </c>
       <c r="G36" s="1" t="str">
         <f>Matches!G13</f>
@@ -6737,9 +6725,9 @@
         <f>Matches!E14</f>
         <v>1</v>
       </c>
-      <c r="F37" s="1" t="str">
+      <c r="F37" s="14">
         <f>Matches!F14</f>
-        <v>16:30</v>
+        <v>0.6875</v>
       </c>
       <c r="G37" s="1" t="str">
         <f>Matches!G14</f>
@@ -6813,9 +6801,9 @@
         <f>Matches!E15</f>
         <v>2</v>
       </c>
-      <c r="F38" s="1" t="str">
+      <c r="F38" s="14">
         <f>Matches!F15</f>
-        <v>16:30</v>
+        <v>0.6875</v>
       </c>
       <c r="G38" s="1" t="str">
         <f>Matches!G15</f>
@@ -6889,9 +6877,9 @@
         <f>Matches!E16</f>
         <v>3 (S)</v>
       </c>
-      <c r="F39" s="1" t="str">
+      <c r="F39" s="14">
         <f>Matches!F16</f>
-        <v>16:30</v>
+        <v>0.6875</v>
       </c>
       <c r="G39" s="1" t="str">
         <f>Matches!G16</f>
@@ -6965,9 +6953,9 @@
         <f>Matches!E17</f>
         <v>1</v>
       </c>
-      <c r="F40" s="1" t="str">
+      <c r="F40" s="14">
         <f>Matches!F17</f>
-        <v>17:00</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="G40" s="1" t="str">
         <f>Matches!G17</f>
@@ -7041,9 +7029,9 @@
         <f>Matches!E18</f>
         <v>2</v>
       </c>
-      <c r="F41" s="1" t="str">
+      <c r="F41" s="14">
         <f>Matches!F18</f>
-        <v>17:00</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="G41" s="1" t="str">
         <f>Matches!G18</f>
@@ -7117,9 +7105,9 @@
         <f>Matches!E19</f>
         <v>3 (S)</v>
       </c>
-      <c r="F42" s="1" t="str">
+      <c r="F42" s="14">
         <f>Matches!F19</f>
-        <v>17:00</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="G42" s="1" t="str">
         <f>Matches!G19</f>
@@ -7193,9 +7181,9 @@
         <f>Matches!E20</f>
         <v>1</v>
       </c>
-      <c r="F43" s="1" t="str">
+      <c r="F43" s="14">
         <f>Matches!F20</f>
-        <v>17:30</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="G43" s="1" t="str">
         <f>Matches!G20</f>
@@ -7269,9 +7257,9 @@
         <f>Matches!E21</f>
         <v>2</v>
       </c>
-      <c r="F44" s="1" t="str">
+      <c r="F44" s="14">
         <f>Matches!F21</f>
-        <v>17:30</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="G44" s="1" t="str">
         <f>Matches!G21</f>
@@ -7345,9 +7333,9 @@
         <f>Matches!E22</f>
         <v>3 (S)</v>
       </c>
-      <c r="F45" s="1" t="str">
+      <c r="F45" s="14">
         <f>Matches!F22</f>
-        <v>17:30</v>
+        <v>0.69930555555555551</v>
       </c>
       <c r="G45" s="1" t="str">
         <f>Matches!G22</f>
@@ -7421,9 +7409,9 @@
         <f>Matches!E23</f>
         <v>1</v>
       </c>
-      <c r="F46" s="1" t="str">
+      <c r="F46" s="14">
         <f>Matches!F23</f>
-        <v>18:00</v>
+        <v>0.75</v>
       </c>
       <c r="G46" s="1" t="str">
         <f>Matches!G23</f>
@@ -7497,9 +7485,9 @@
         <f>Matches!E24</f>
         <v>2</v>
       </c>
-      <c r="F47" s="1" t="str">
+      <c r="F47" s="14">
         <f>Matches!F24</f>
-        <v>18:00</v>
+        <v>0.75</v>
       </c>
       <c r="G47" s="1" t="str">
         <f>Matches!G24</f>
@@ -7573,9 +7561,9 @@
         <f>Matches!E25</f>
         <v>3 (S)</v>
       </c>
-      <c r="F48" s="1" t="str">
+      <c r="F48" s="14">
         <f>Matches!F25</f>
-        <v>18:00</v>
+        <v>0.75</v>
       </c>
       <c r="G48" s="1" t="str">
         <f>Matches!G25</f>
@@ -7710,7 +7698,7 @@
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="B51" s="10"/>
       <c r="C51" s="10"/>
@@ -7752,22 +7740,22 @@
     </row>
     <row r="52" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -7802,7 +7790,7 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="str">
         <f>IF(Goals!A2="","",Goals!A2)</f>
         <v>M01</v>
@@ -7860,18 +7848,18 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="str">
         <f>IF(Goals!A3="","",Goals!A3)</f>
         <v>M01</v>
       </c>
       <c r="B54" s="1" t="str">
         <f>IF(Goals!A3="","",Goals!B3)</f>
-        <v>Boldò Glimt</v>
+        <v>All Blacks</v>
       </c>
       <c r="C54" s="1">
         <f>IF(Goals!A3="","",Goals!C3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" s="1" t="str">
         <f>IF(Goals!A3="","",Goals!D3)</f>
@@ -7879,11 +7867,11 @@
       </c>
       <c r="E54" s="1" t="str">
         <f>IF(Goals!A3="","",Goals!E3)</f>
-        <v>7 - ANGELO REDI</v>
+        <v>9 - NICOLÒ BERGANTIN</v>
       </c>
       <c r="F54" s="1" t="str">
         <f>IF(Goals!A3="","",Goals!F3)</f>
-        <v>Boldò Glimt</v>
+        <v>All Blacks</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
@@ -7921,27 +7909,27 @@
     <row r="55" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="str">
         <f>IF(Goals!A4="","",Goals!A4)</f>
-        <v/>
+        <v>M01</v>
       </c>
       <c r="B55" s="1" t="str">
         <f>IF(Goals!A4="","",Goals!B4)</f>
-        <v/>
-      </c>
-      <c r="C55" s="1" t="str">
+        <v>All Blacks</v>
+      </c>
+      <c r="C55" s="1">
         <f>IF(Goals!A4="","",Goals!C4)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="D55" s="1" t="str">
         <f>IF(Goals!A4="","",Goals!D4)</f>
-        <v/>
+        <v>Goal</v>
       </c>
       <c r="E55" s="1" t="str">
         <f>IF(Goals!A4="","",Goals!E4)</f>
-        <v/>
+        <v>8 - DAVIDE GIRARDELLO</v>
       </c>
       <c r="F55" s="1" t="str">
         <f>IF(Goals!A4="","",Goals!F4)</f>
-        <v/>
+        <v>All Blacks</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
@@ -7979,27 +7967,27 @@
     <row r="56" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="str">
         <f>IF(Goals!A5="","",Goals!A5)</f>
-        <v/>
+        <v>M01</v>
       </c>
       <c r="B56" s="1" t="str">
         <f>IF(Goals!A5="","",Goals!B5)</f>
-        <v/>
-      </c>
-      <c r="C56" s="1" t="str">
+        <v>All Blacks</v>
+      </c>
+      <c r="C56" s="1">
         <f>IF(Goals!A5="","",Goals!C5)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>IF(Goals!A5="","",Goals!D5)</f>
-        <v/>
+        <v>Goal</v>
       </c>
       <c r="E56" s="1" t="str">
         <f>IF(Goals!A5="","",Goals!E5)</f>
-        <v/>
+        <v>8 - DAVIDE GIRARDELLO</v>
       </c>
       <c r="F56" s="1" t="str">
         <f>IF(Goals!A5="","",Goals!F5)</f>
-        <v/>
+        <v>All Blacks</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
@@ -8034,30 +8022,30 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="str">
         <f>IF(Goals!A6="","",Goals!A6)</f>
-        <v/>
+        <v>M01</v>
       </c>
       <c r="B57" s="1" t="str">
         <f>IF(Goals!A6="","",Goals!B6)</f>
-        <v/>
-      </c>
-      <c r="C57" s="1" t="str">
+        <v>Boldò Glimt</v>
+      </c>
+      <c r="C57" s="1">
         <f>IF(Goals!A6="","",Goals!C6)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>IF(Goals!A6="","",Goals!D6)</f>
-        <v/>
+        <v>Goal</v>
       </c>
       <c r="E57" s="1" t="str">
         <f>IF(Goals!A6="","",Goals!E6)</f>
-        <v/>
+        <v>7 - ANGELO REDI</v>
       </c>
       <c r="F57" s="1" t="str">
         <f>IF(Goals!A6="","",Goals!F6)</f>
-        <v/>
+        <v>Boldò Glimt</v>
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
@@ -8095,27 +8083,27 @@
     <row r="58" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="str">
         <f>IF(Goals!A7="","",Goals!A7)</f>
-        <v/>
+        <v>M01</v>
       </c>
       <c r="B58" s="1" t="str">
         <f>IF(Goals!A7="","",Goals!B7)</f>
-        <v/>
-      </c>
-      <c r="C58" s="1" t="str">
+        <v>Boldò Glimt</v>
+      </c>
+      <c r="C58" s="1">
         <f>IF(Goals!A7="","",Goals!C7)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D58" s="1" t="str">
         <f>IF(Goals!A7="","",Goals!D7)</f>
-        <v/>
+        <v>Goal</v>
       </c>
       <c r="E58" s="1" t="str">
         <f>IF(Goals!A7="","",Goals!E7)</f>
-        <v/>
+        <v>7 - ANGELO REDI</v>
       </c>
       <c r="F58" s="1" t="str">
         <f>IF(Goals!A7="","",Goals!F7)</f>
-        <v/>
+        <v>Boldò Glimt</v>
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -8498,7 +8486,7 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
     </row>
-    <row r="65" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="str">
         <f>IF(Goals!A14="","",Goals!A14)</f>
         <v>M02</v>
@@ -8556,7 +8544,7 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row r="66" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="str">
         <f>IF(Goals!A15="","",Goals!A15)</f>
         <v>M02</v>
@@ -8614,7 +8602,7 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row r="67" spans="1:26" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="str">
         <f>IF(Goals!A16="","",Goals!A16)</f>
         <v>M02</v>
@@ -8672,7 +8660,7 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="str">
         <f>IF(Goals!A17="","",Goals!A17)</f>
         <v>M02</v>
@@ -8788,7 +8776,7 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row r="70" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="str">
         <f>IF(Goals!A19="","",Goals!A19)</f>
         <v>M02</v>
@@ -9842,7 +9830,7 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="str">
         <f>IF(Goals!A38="","",Goals!A38)</f>
         <v>M04</v>
@@ -9888,7 +9876,7 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
     </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="str">
         <f>IF(Goals!A39="","",Goals!A39)</f>
         <v>M04</v>
@@ -9934,7 +9922,7 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="str">
         <f>IF(Goals!A40="","",Goals!A40)</f>
         <v>M04</v>
@@ -9980,7 +9968,7 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="str">
         <f>IF(Goals!A41="","",Goals!A41)</f>
         <v>M04</v>
@@ -10026,7 +10014,7 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="str">
         <f>IF(Goals!A42="","",Goals!A42)</f>
         <v>M04</v>
@@ -10394,7 +10382,7 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="str">
         <f>IF(Goals!A50="","",Goals!A50)</f>
         <v>M05</v>
@@ -10440,7 +10428,7 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row r="102" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="str">
         <f>IF(Goals!A51="","",Goals!A51)</f>
         <v>M05</v>
@@ -10486,7 +10474,7 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row r="103" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="str">
         <f>IF(Goals!A52="","",Goals!A52)</f>
         <v>M05</v>
@@ -10532,7 +10520,7 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="str">
         <f>IF(Goals!A53="","",Goals!A53)</f>
         <v>M05</v>
@@ -10946,7 +10934,7 @@
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
     </row>
-    <row r="113" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="str">
         <f>IF(Goals!A62="","",Goals!A62)</f>
         <v>M06</v>
@@ -12050,7 +12038,7 @@
       <c r="Y136" s="1"/>
       <c r="Z136" s="1"/>
     </row>
-    <row r="137" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="str">
         <f>IF(Goals!A86="","",Goals!A86)</f>
         <v>M08</v>
@@ -12096,7 +12084,7 @@
       <c r="Y137" s="1"/>
       <c r="Z137" s="1"/>
     </row>
-    <row r="138" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="str">
         <f>IF(Goals!A87="","",Goals!A87)</f>
         <v>M08</v>
@@ -12142,7 +12130,7 @@
       <c r="Y138" s="1"/>
       <c r="Z138" s="1"/>
     </row>
-    <row r="139" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="str">
         <f>IF(Goals!A88="","",Goals!A88)</f>
         <v>M08</v>
@@ -12188,7 +12176,7 @@
       <c r="Y139" s="1"/>
       <c r="Z139" s="1"/>
     </row>
-    <row r="140" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="str">
         <f>IF(Goals!A89="","",Goals!A89)</f>
         <v>M08</v>
@@ -12234,7 +12222,7 @@
       <c r="Y140" s="1"/>
       <c r="Z140" s="1"/>
     </row>
-    <row r="141" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="str">
         <f>IF(Goals!A90="","",Goals!A90)</f>
         <v>M08</v>
@@ -12280,7 +12268,7 @@
       <c r="Y141" s="1"/>
       <c r="Z141" s="1"/>
     </row>
-    <row r="142" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="str">
         <f>IF(Goals!A91="","",Goals!A91)</f>
         <v>M08</v>
@@ -12326,7 +12314,7 @@
       <c r="Y142" s="1"/>
       <c r="Z142" s="1"/>
     </row>
-    <row r="143" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="str">
         <f>IF(Goals!A92="","",Goals!A92)</f>
         <v>M08</v>
@@ -12740,7 +12728,7 @@
       <c r="Y151" s="1"/>
       <c r="Z151" s="1"/>
     </row>
-    <row r="152" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="str">
         <f>IF(Goals!A101="","",Goals!A101)</f>
         <v>M09</v>
@@ -12786,7 +12774,7 @@
       <c r="Y152" s="1"/>
       <c r="Z152" s="1"/>
     </row>
-    <row r="153" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="str">
         <f>IF(Goals!A102="","",Goals!A102)</f>
         <v>M09</v>
@@ -12832,7 +12820,7 @@
       <c r="Y153" s="1"/>
       <c r="Z153" s="1"/>
     </row>
-    <row r="154" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="str">
         <f>IF(Goals!A103="","",Goals!A103)</f>
         <v>M09</v>
@@ -12878,7 +12866,7 @@
       <c r="Y154" s="1"/>
       <c r="Z154" s="1"/>
     </row>
-    <row r="155" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="str">
         <f>IF(Goals!A104="","",Goals!A104)</f>
         <v>M09</v>
@@ -13200,7 +13188,7 @@
       <c r="Y161" s="1"/>
       <c r="Z161" s="1"/>
     </row>
-    <row r="162" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="str">
         <f>IF(Goals!A111="","",Goals!A111)</f>
         <v>M10</v>
@@ -13246,7 +13234,7 @@
       <c r="Y162" s="1"/>
       <c r="Z162" s="1"/>
     </row>
-    <row r="163" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="str">
         <f>IF(Goals!A112="","",Goals!A112)</f>
         <v>M10</v>
@@ -13292,7 +13280,7 @@
       <c r="Y163" s="1"/>
       <c r="Z163" s="1"/>
     </row>
-    <row r="164" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="str">
         <f>IF(Goals!A113="","",Goals!A113)</f>
         <v>M10</v>
@@ -13338,7 +13326,7 @@
       <c r="Y164" s="1"/>
       <c r="Z164" s="1"/>
     </row>
-    <row r="165" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="str">
         <f>IF(Goals!A114="","",Goals!A114)</f>
         <v>M10</v>
@@ -28912,7 +28900,8 @@
   <dimension ref="A1:Z25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="18" customWidth="1"/>
+    <col min="1" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="18" style="12" customWidth="1"/>
     <col min="7" max="8" width="28" customWidth="1"/>
     <col min="9" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="28" customWidth="1"/>
@@ -28936,7 +28925,7 @@
       <c r="E1" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="11" t="s">
         <v>520</v>
       </c>
       <c r="G1" s="5" t="s">
@@ -28996,8 +28985,8 @@
       <c r="E2" t="s">
         <v>531</v>
       </c>
-      <c r="F2" t="s">
-        <v>532</v>
+      <c r="F2" s="13">
+        <v>0.69861111111111107</v>
       </c>
       <c r="G2" t="s">
         <v>62</v>
@@ -29006,38 +28995,36 @@
         <v>64</v>
       </c>
       <c r="I2" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J2" s="2">
-        <v>1</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>64</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K2" s="2"/>
       <c r="L2" t="str">
         <f t="shared" ref="L2:L25" si="0">IF(OR(I2="",J2=""),"Pending",IF(I2=J2,IF(K2="","Needs penalty winner","Complete"),"Complete"))</f>
         <v>Complete</v>
       </c>
       <c r="M2">
         <f>IF(OR(I2="",J2=""),"",IF(I2&gt;J2,Settings!$B$2,IF(I2&lt;J2,Settings!$B$5,IF(K2=G2,Settings!$B$3,IF(K2=H2,Settings!$B$4,"")))))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N2">
         <f>IF(OR(I2="",J2=""),"",IF(J2&gt;I2,Settings!$B$2,IF(J2&lt;I2,Settings!$B$5,IF(K2=H2,Settings!$B$3,IF(K2=G2,Settings!$B$4,"")))))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O2" t="str">
         <f t="shared" ref="O2:O25" si="1">IF(OR(I2="",J2=""),"",IF(I2&gt;J2,G2,IF(J2&gt;I2,H2,K2)))</f>
-        <v>Boldò Glimt</v>
+        <v>All Blacks</v>
       </c>
       <c r="P2" t="str">
         <f t="shared" ref="P2:P25" si="2">IF(OR(I2="",J2=""),"",G2&amp;" "&amp;I2&amp;" - "&amp;J2&amp;" "&amp;H2&amp;IF(K2&lt;&gt;""," (rigori: "&amp;K2&amp;")",""))</f>
-        <v>All Blacks 1 - 1 Boldò Glimt (rigori: Boldò Glimt)</v>
+        <v>All Blacks 4 - 2 Boldò Glimt</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B3" t="s">
         <v>30</v>
@@ -29049,10 +29036,10 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>534</v>
-      </c>
-      <c r="F3" t="s">
-        <v>532</v>
+        <v>533</v>
+      </c>
+      <c r="F3" s="13">
+        <v>0.59375</v>
       </c>
       <c r="G3" t="s">
         <v>66</v>
@@ -29090,7 +29077,7 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B4" t="s">
         <v>30</v>
@@ -29102,10 +29089,10 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>536</v>
-      </c>
-      <c r="F4" t="s">
-        <v>532</v>
+        <v>535</v>
+      </c>
+      <c r="F4" s="13">
+        <v>0.59375</v>
       </c>
       <c r="G4" t="s">
         <v>44</v>
@@ -29143,7 +29130,7 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B5" t="s">
         <v>30</v>
@@ -29157,8 +29144,8 @@
       <c r="E5" t="s">
         <v>531</v>
       </c>
-      <c r="F5" t="s">
-        <v>538</v>
+      <c r="F5" s="13">
+        <v>0.61458333333333337</v>
       </c>
       <c r="G5" t="s">
         <v>53</v>
@@ -29196,7 +29183,7 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B6" t="s">
         <v>30</v>
@@ -29208,10 +29195,10 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>534</v>
-      </c>
-      <c r="F6" t="s">
-        <v>538</v>
+        <v>533</v>
+      </c>
+      <c r="F6" s="13">
+        <v>0.61458333333333337</v>
       </c>
       <c r="G6" t="s">
         <v>57</v>
@@ -29251,7 +29238,7 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
@@ -29263,10 +29250,10 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>536</v>
-      </c>
-      <c r="F7" t="s">
-        <v>538</v>
+        <v>535</v>
+      </c>
+      <c r="F7" s="13">
+        <v>0.61458333333333337</v>
       </c>
       <c r="G7" t="s">
         <v>48</v>
@@ -29304,7 +29291,7 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
@@ -29318,8 +29305,8 @@
       <c r="E8" t="s">
         <v>531</v>
       </c>
-      <c r="F8" t="s">
-        <v>542</v>
+      <c r="F8" s="13">
+        <v>0.63541666666666663</v>
       </c>
       <c r="G8" t="s">
         <v>35</v>
@@ -29357,7 +29344,7 @@
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
@@ -29369,10 +29356,10 @@
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>534</v>
-      </c>
-      <c r="F9" t="s">
-        <v>542</v>
+        <v>533</v>
+      </c>
+      <c r="F9" s="13">
+        <v>0.63541666666666663</v>
       </c>
       <c r="G9" t="s">
         <v>39</v>
@@ -29410,7 +29397,7 @@
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
@@ -29422,10 +29409,10 @@
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>536</v>
-      </c>
-      <c r="F10" t="s">
-        <v>542</v>
+        <v>535</v>
+      </c>
+      <c r="F10" s="13">
+        <v>0.63541666666666663</v>
       </c>
       <c r="G10" t="s">
         <v>62</v>
@@ -29463,7 +29450,7 @@
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
@@ -29477,8 +29464,8 @@
       <c r="E11" t="s">
         <v>531</v>
       </c>
-      <c r="F11" t="s">
-        <v>546</v>
+      <c r="F11" s="13">
+        <v>0.65625</v>
       </c>
       <c r="G11" t="s">
         <v>44</v>
@@ -29516,7 +29503,7 @@
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
@@ -29528,10 +29515,10 @@
         <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>534</v>
-      </c>
-      <c r="F12" t="s">
-        <v>546</v>
+        <v>533</v>
+      </c>
+      <c r="F12" s="13">
+        <v>0.65625</v>
       </c>
       <c r="G12" t="s">
         <v>46</v>
@@ -29565,7 +29552,7 @@
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
@@ -29577,10 +29564,10 @@
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>536</v>
-      </c>
-      <c r="F13" t="s">
-        <v>546</v>
+        <v>535</v>
+      </c>
+      <c r="F13" s="13">
+        <v>0.65625</v>
       </c>
       <c r="G13" t="s">
         <v>64</v>
@@ -29614,7 +29601,7 @@
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
@@ -29628,8 +29615,8 @@
       <c r="E14" t="s">
         <v>531</v>
       </c>
-      <c r="F14" t="s">
-        <v>550</v>
+      <c r="F14" s="13">
+        <v>0.6875</v>
       </c>
       <c r="G14" t="s">
         <v>53</v>
@@ -29663,7 +29650,7 @@
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="B15" t="s">
         <v>30</v>
@@ -29675,10 +29662,10 @@
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>534</v>
-      </c>
-      <c r="F15" t="s">
-        <v>550</v>
+        <v>533</v>
+      </c>
+      <c r="F15" s="13">
+        <v>0.6875</v>
       </c>
       <c r="G15" t="s">
         <v>55</v>
@@ -29712,7 +29699,7 @@
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="B16" t="s">
         <v>30</v>
@@ -29724,10 +29711,10 @@
         <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>536</v>
-      </c>
-      <c r="F16" t="s">
-        <v>550</v>
+        <v>535</v>
+      </c>
+      <c r="F16" s="13">
+        <v>0.6875</v>
       </c>
       <c r="G16" t="s">
         <v>35</v>
@@ -29761,7 +29748,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="B17" t="s">
         <v>30</v>
@@ -29775,8 +29762,8 @@
       <c r="E17" t="s">
         <v>531</v>
       </c>
-      <c r="F17" t="s">
-        <v>554</v>
+      <c r="F17" s="13">
+        <v>0.70833333333333337</v>
       </c>
       <c r="G17" t="s">
         <v>62</v>
@@ -29810,7 +29797,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="B18" t="s">
         <v>30</v>
@@ -29822,10 +29809,10 @@
         <v>3</v>
       </c>
       <c r="E18" t="s">
-        <v>534</v>
-      </c>
-      <c r="F18" t="s">
-        <v>554</v>
+        <v>533</v>
+      </c>
+      <c r="F18" s="13">
+        <v>0.70833333333333337</v>
       </c>
       <c r="G18" t="s">
         <v>64</v>
@@ -29859,7 +29846,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="B19" t="s">
         <v>30</v>
@@ -29871,10 +29858,10 @@
         <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>536</v>
-      </c>
-      <c r="F19" t="s">
-        <v>554</v>
+        <v>535</v>
+      </c>
+      <c r="F19" s="13">
+        <v>0.70833333333333337</v>
       </c>
       <c r="G19" t="s">
         <v>37</v>
@@ -29908,7 +29895,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="B20" t="s">
         <v>30</v>
@@ -29922,8 +29909,8 @@
       <c r="E20" t="s">
         <v>531</v>
       </c>
-      <c r="F20" t="s">
-        <v>558</v>
+      <c r="F20" s="13">
+        <v>0.72916666666666663</v>
       </c>
       <c r="G20" t="s">
         <v>44</v>
@@ -29957,7 +29944,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="B21" t="s">
         <v>30</v>
@@ -29969,10 +29956,10 @@
         <v>3</v>
       </c>
       <c r="E21" t="s">
-        <v>534</v>
-      </c>
-      <c r="F21" t="s">
-        <v>558</v>
+        <v>533</v>
+      </c>
+      <c r="F21" s="13">
+        <v>0.72916666666666663</v>
       </c>
       <c r="G21" t="s">
         <v>46</v>
@@ -30006,7 +29993,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="B22" t="s">
         <v>30</v>
@@ -30018,10 +30005,10 @@
         <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>536</v>
-      </c>
-      <c r="F22" t="s">
-        <v>558</v>
+        <v>535</v>
+      </c>
+      <c r="F22" s="13">
+        <v>0.69930555555555551</v>
       </c>
       <c r="G22" t="s">
         <v>53</v>
@@ -30055,7 +30042,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="B23" t="s">
         <v>30</v>
@@ -30069,8 +30056,8 @@
       <c r="E23" t="s">
         <v>531</v>
       </c>
-      <c r="F23" t="s">
-        <v>562</v>
+      <c r="F23" s="13">
+        <v>0.75</v>
       </c>
       <c r="G23" t="s">
         <v>35</v>
@@ -30104,7 +30091,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="B24" t="s">
         <v>30</v>
@@ -30116,10 +30103,10 @@
         <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>534</v>
-      </c>
-      <c r="F24" t="s">
-        <v>562</v>
+        <v>533</v>
+      </c>
+      <c r="F24" s="13">
+        <v>0.75</v>
       </c>
       <c r="G24" t="s">
         <v>37</v>
@@ -30153,7 +30140,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="B25" t="s">
         <v>30</v>
@@ -30165,10 +30152,10 @@
         <v>3</v>
       </c>
       <c r="E25" t="s">
-        <v>536</v>
-      </c>
-      <c r="F25" t="s">
-        <v>562</v>
+        <v>535</v>
+      </c>
+      <c r="F25" s="13">
+        <v>0.75</v>
       </c>
       <c r="G25" t="s">
         <v>55</v>
@@ -30201,7 +30188,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" sqref="K2:K25" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>$G2:$H2</formula1>
     </dataValidation>
@@ -30226,34 +30213,34 @@
         <v>516</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>18</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>525</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
@@ -30312,7 +30299,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
@@ -30322,22 +30309,22 @@
       </c>
       <c r="B3" t="str">
         <f>IF(A3="","",IF(J3&lt;=INDEX(Matches!$I$2:$I$25,I3-1),INDEX(Matches!$G$2:$G$25,I3-1),INDEX(Matches!$H$2:$H$25,I3-1)))</f>
-        <v>Boldò Glimt</v>
+        <v>All Blacks</v>
       </c>
       <c r="C3">
         <f>IF(A3="","",COUNTIFS($A$2:A3,A3,$B$2:B3,B3))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Goal</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>438</v>
+        <v>417</v>
       </c>
       <c r="F3" t="str">
         <f t="shared" si="1"/>
-        <v>Boldò Glimt</v>
+        <v>All Blacks</v>
       </c>
       <c r="G3" t="str">
         <f t="shared" si="2"/>
@@ -30345,7 +30332,7 @@
       </c>
       <c r="H3" t="str">
         <f>IF(F3="","",VLOOKUP(F3,Validation!$A$2:$B$17,2,FALSE))</f>
-        <v>Validation!$P$2:$P$11</v>
+        <v>Validation!$O$2:$O$12</v>
       </c>
       <c r="I3">
         <f>INT((ROW()-2)/Settings!$B$6)+2</f>
@@ -30359,32 +30346,34 @@
     <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>IF(OR(INDEX(Matches!$I$2:$I$25,I4-1)="",INDEX(Matches!$J$2:$J$25,I4-1)=""),"",IF(J4&lt;=INDEX(Matches!$I$2:$I$25,I4-1)+INDEX(Matches!$J$2:$J$25,I4-1),INDEX(Matches!$A$2:$A$25,I4-1),""))</f>
-        <v/>
+        <v>M01</v>
       </c>
       <c r="B4" t="str">
         <f>IF(A4="","",IF(J4&lt;=INDEX(Matches!$I$2:$I$25,I4-1),INDEX(Matches!$G$2:$G$25,I4-1),INDEX(Matches!$H$2:$H$25,I4-1)))</f>
-        <v/>
-      </c>
-      <c r="C4" t="str">
+        <v>All Blacks</v>
+      </c>
+      <c r="C4">
         <f>IF(A4="","",COUNTIFS($A$2:A4,A4,$B$2:B4,B4))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="D4" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E4" s="2"/>
+        <v>Goal</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>414</v>
+      </c>
       <c r="F4" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>All Blacks</v>
       </c>
       <c r="G4" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="H4" t="str">
         <f>IF(F4="","",VLOOKUP(F4,Validation!$A$2:$B$17,2,FALSE))</f>
-        <v/>
+        <v>Validation!$O$2:$O$12</v>
       </c>
       <c r="I4">
         <f>INT((ROW()-2)/Settings!$B$6)+2</f>
@@ -30398,32 +30387,34 @@
     <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>IF(OR(INDEX(Matches!$I$2:$I$25,I5-1)="",INDEX(Matches!$J$2:$J$25,I5-1)=""),"",IF(J5&lt;=INDEX(Matches!$I$2:$I$25,I5-1)+INDEX(Matches!$J$2:$J$25,I5-1),INDEX(Matches!$A$2:$A$25,I5-1),""))</f>
-        <v/>
+        <v>M01</v>
       </c>
       <c r="B5" t="str">
         <f>IF(A5="","",IF(J5&lt;=INDEX(Matches!$I$2:$I$25,I5-1),INDEX(Matches!$G$2:$G$25,I5-1),INDEX(Matches!$H$2:$H$25,I5-1)))</f>
-        <v/>
-      </c>
-      <c r="C5" t="str">
+        <v>All Blacks</v>
+      </c>
+      <c r="C5">
         <f>IF(A5="","",COUNTIFS($A$2:A5,A5,$B$2:B5,B5))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="D5" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E5" s="2"/>
+        <v>Goal</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>414</v>
+      </c>
       <c r="F5" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>All Blacks</v>
       </c>
       <c r="G5" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="H5" t="str">
         <f>IF(F5="","",VLOOKUP(F5,Validation!$A$2:$B$17,2,FALSE))</f>
-        <v/>
+        <v>Validation!$O$2:$O$12</v>
       </c>
       <c r="I5">
         <f>INT((ROW()-2)/Settings!$B$6)+2</f>
@@ -30437,32 +30428,34 @@
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>IF(OR(INDEX(Matches!$I$2:$I$25,I6-1)="",INDEX(Matches!$J$2:$J$25,I6-1)=""),"",IF(J6&lt;=INDEX(Matches!$I$2:$I$25,I6-1)+INDEX(Matches!$J$2:$J$25,I6-1),INDEX(Matches!$A$2:$A$25,I6-1),""))</f>
-        <v/>
+        <v>M01</v>
       </c>
       <c r="B6" t="str">
         <f>IF(A6="","",IF(J6&lt;=INDEX(Matches!$I$2:$I$25,I6-1),INDEX(Matches!$G$2:$G$25,I6-1),INDEX(Matches!$H$2:$H$25,I6-1)))</f>
-        <v/>
-      </c>
-      <c r="C6" t="str">
+        <v>Boldò Glimt</v>
+      </c>
+      <c r="C6">
         <f>IF(A6="","",COUNTIFS($A$2:A6,A6,$B$2:B6,B6))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D6" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E6" s="2"/>
+        <v>Goal</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>438</v>
+      </c>
       <c r="F6" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Boldò Glimt</v>
       </c>
       <c r="G6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="H6" t="str">
         <f>IF(F6="","",VLOOKUP(F6,Validation!$A$2:$B$17,2,FALSE))</f>
-        <v/>
+        <v>Validation!$P$2:$P$11</v>
       </c>
       <c r="I6">
         <f>INT((ROW()-2)/Settings!$B$6)+2</f>
@@ -30476,32 +30469,34 @@
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>IF(OR(INDEX(Matches!$I$2:$I$25,I7-1)="",INDEX(Matches!$J$2:$J$25,I7-1)=""),"",IF(J7&lt;=INDEX(Matches!$I$2:$I$25,I7-1)+INDEX(Matches!$J$2:$J$25,I7-1),INDEX(Matches!$A$2:$A$25,I7-1),""))</f>
-        <v/>
+        <v>M01</v>
       </c>
       <c r="B7" t="str">
         <f>IF(A7="","",IF(J7&lt;=INDEX(Matches!$I$2:$I$25,I7-1),INDEX(Matches!$G$2:$G$25,I7-1),INDEX(Matches!$H$2:$H$25,I7-1)))</f>
-        <v/>
-      </c>
-      <c r="C7" t="str">
+        <v>Boldò Glimt</v>
+      </c>
+      <c r="C7">
         <f>IF(A7="","",COUNTIFS($A$2:A7,A7,$B$2:B7,B7))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D7" s="2" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E7" s="2"/>
+        <v>Goal</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>438</v>
+      </c>
       <c r="F7" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Boldò Glimt</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="H7" t="str">
         <f>IF(F7="","",VLOOKUP(F7,Validation!$A$2:$B$17,2,FALSE))</f>
-        <v/>
+        <v>Validation!$P$2:$P$11</v>
       </c>
       <c r="I7">
         <f>INT((ROW()-2)/Settings!$B$6)+2</f>
@@ -31240,7 +31235,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>215</v>
@@ -44434,19 +44429,19 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>73</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
@@ -46800,11 +46795,11 @@
       </c>
       <c r="D124">
         <f>COUNTIFS(Goals!$D$2:$D$361,"Goal",Goals!$E$2:$E$361,C124,Goals!$F$2:$F$361,B124)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E124">
         <f t="shared" si="3"/>
-        <v>-0.124</v>
+        <v>199999.87599999999</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
@@ -46819,11 +46814,11 @@
       </c>
       <c r="D125">
         <f>COUNTIFS(Goals!$D$2:$D$361,"Goal",Goals!$E$2:$E$361,C125,Goals!$F$2:$F$361,B125)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E125">
         <f t="shared" si="3"/>
-        <v>-0.125</v>
+        <v>99999.875</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
@@ -46952,11 +46947,11 @@
       </c>
       <c r="D132">
         <f>COUNTIFS(Goals!$D$2:$D$361,"Goal",Goals!$E$2:$E$361,C132,Goals!$F$2:$F$361,B132)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E132">
         <f t="shared" si="4"/>
-        <v>99999.868000000002</v>
+        <v>199999.86799999999</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
@@ -47468,16 +47463,16 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>567</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>574</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>575</v>
       </c>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
@@ -47563,11 +47558,11 @@
       </c>
       <c r="B5" t="str">
         <f>IF($A5="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A5),ScorerData!$E$2:$E$158,0)))</f>
-        <v>LUCA CAVALLARO</v>
+        <v>DAVIDE GIRARDELLO</v>
       </c>
       <c r="C5" t="str">
         <f>IF($A5="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A5),ScorerData!$E$2:$E$158,0)))</f>
-        <v>Coca Juniors</v>
+        <v>All Blacks</v>
       </c>
       <c r="D5">
         <f>IF($A5="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A5),ScorerData!$E$2:$E$158,0)))</f>
@@ -47581,11 +47576,11 @@
       </c>
       <c r="B6" t="str">
         <f>IF($A6="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A6),ScorerData!$E$2:$E$158,0)))</f>
-        <v>KEVIN DOBROZI</v>
+        <v>ANGELO REDI</v>
       </c>
       <c r="C6" t="str">
         <f>IF($A6="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A6),ScorerData!$E$2:$E$158,0)))</f>
-        <v>Coca Juniors</v>
+        <v>Boldò Glimt</v>
       </c>
       <c r="D6">
         <f>IF($A6="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A6),ScorerData!$E$2:$E$158,0)))</f>
@@ -47599,7 +47594,7 @@
       </c>
       <c r="B7" t="str">
         <f>IF($A7="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A7),ScorerData!$E$2:$E$158,0)))</f>
-        <v>TOMMASO PAVAN</v>
+        <v>LUCA CAVALLARO</v>
       </c>
       <c r="C7" t="str">
         <f>IF($A7="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A7),ScorerData!$E$2:$E$158,0)))</f>
@@ -47617,7 +47612,7 @@
       </c>
       <c r="B8" t="str">
         <f>IF($A8="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A8),ScorerData!$E$2:$E$158,0)))</f>
-        <v>GIAN MARCO MARANGONI</v>
+        <v>KEVIN DOBROZI</v>
       </c>
       <c r="C8" t="str">
         <f>IF($A8="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A8),ScorerData!$E$2:$E$158,0)))</f>
@@ -47635,15 +47630,15 @@
       </c>
       <c r="B9" t="str">
         <f>IF($A9="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A9),ScorerData!$E$2:$E$158,0)))</f>
-        <v>GIOVANNI BALLO</v>
+        <v>TOMMASO PAVAN</v>
       </c>
       <c r="C9" t="str">
         <f>IF($A9="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A9),ScorerData!$E$2:$E$158,0)))</f>
-        <v>Fatine FC</v>
+        <v>Coca Juniors</v>
       </c>
       <c r="D9">
         <f>IF($A9="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A9),ScorerData!$E$2:$E$158,0)))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.3">
@@ -47653,15 +47648,15 @@
       </c>
       <c r="B10" t="str">
         <f>IF($A10="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A10),ScorerData!$E$2:$E$158,0)))</f>
-        <v>DANIELE MARZOLLA</v>
+        <v>GIAN MARCO MARANGONI</v>
       </c>
       <c r="C10" t="str">
         <f>IF($A10="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A10),ScorerData!$E$2:$E$158,0)))</f>
-        <v>Fatine FC</v>
+        <v>Coca Juniors</v>
       </c>
       <c r="D10">
         <f>IF($A10="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A10),ScorerData!$E$2:$E$158,0)))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.3">
@@ -47671,7 +47666,7 @@
       </c>
       <c r="B11" t="str">
         <f>IF($A11="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A11),ScorerData!$E$2:$E$158,0)))</f>
-        <v>NICHOLAS MILAN</v>
+        <v>GIOVANNI BALLO</v>
       </c>
       <c r="C11" t="str">
         <f>IF($A11="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A11),ScorerData!$E$2:$E$158,0)))</f>
@@ -47689,7 +47684,7 @@
       </c>
       <c r="B12" t="str">
         <f>IF($A12="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A12),ScorerData!$E$2:$E$158,0)))</f>
-        <v>ALESSIO MILAN</v>
+        <v>DANIELE MARZOLLA</v>
       </c>
       <c r="C12" t="str">
         <f>IF($A12="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A12),ScorerData!$E$2:$E$158,0)))</f>
@@ -47707,7 +47702,7 @@
       </c>
       <c r="B13" t="str">
         <f>IF($A13="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A13),ScorerData!$E$2:$E$158,0)))</f>
-        <v>NICOLA MARINI</v>
+        <v>NICHOLAS MILAN</v>
       </c>
       <c r="C13" t="str">
         <f>IF($A13="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A13),ScorerData!$E$2:$E$158,0)))</f>
@@ -47725,7 +47720,7 @@
       </c>
       <c r="B14" t="str">
         <f>IF($A14="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A14),ScorerData!$E$2:$E$158,0)))</f>
-        <v>LUCA ROSSETTO</v>
+        <v>ALESSIO MILAN</v>
       </c>
       <c r="C14" t="str">
         <f>IF($A14="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A14),ScorerData!$E$2:$E$158,0)))</f>
@@ -47743,11 +47738,11 @@
       </c>
       <c r="B15" t="str">
         <f>IF($A15="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A15),ScorerData!$E$2:$E$158,0)))</f>
-        <v>LUCA BACCO</v>
+        <v>NICOLA MARINI</v>
       </c>
       <c r="C15" t="str">
         <f>IF($A15="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A15),ScorerData!$E$2:$E$158,0)))</f>
-        <v>Moviola Utd</v>
+        <v>Fatine FC</v>
       </c>
       <c r="D15">
         <f>IF($A15="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A15),ScorerData!$E$2:$E$158,0)))</f>
@@ -47761,11 +47756,11 @@
       </c>
       <c r="B16" t="str">
         <f>IF($A16="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A16),ScorerData!$E$2:$E$158,0)))</f>
-        <v>FILIPPO SCARANELLO</v>
+        <v>LUCA ROSSETTO</v>
       </c>
       <c r="C16" t="str">
         <f>IF($A16="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A16),ScorerData!$E$2:$E$158,0)))</f>
-        <v>Moviola Utd</v>
+        <v>Fatine FC</v>
       </c>
       <c r="D16">
         <f>IF($A16="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A16),ScorerData!$E$2:$E$158,0)))</f>
@@ -47779,11 +47774,11 @@
       </c>
       <c r="B17" t="str">
         <f>IF($A17="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A17),ScorerData!$E$2:$E$158,0)))</f>
-        <v>GIANLUCA PAVAN</v>
+        <v>LUCA BACCO</v>
       </c>
       <c r="C17" t="str">
         <f>IF($A17="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A17),ScorerData!$E$2:$E$158,0)))</f>
-        <v>Astolfi Impianti Elettrici</v>
+        <v>Moviola Utd</v>
       </c>
       <c r="D17">
         <f>IF($A17="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A17),ScorerData!$E$2:$E$158,0)))</f>
@@ -47797,11 +47792,11 @@
       </c>
       <c r="B18" t="str">
         <f>IF($A18="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A18),ScorerData!$E$2:$E$158,0)))</f>
-        <v>ELIA NAGLIERI</v>
+        <v>FILIPPO SCARANELLO</v>
       </c>
       <c r="C18" t="str">
         <f>IF($A18="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A18),ScorerData!$E$2:$E$158,0)))</f>
-        <v>Astolfi Impianti Elettrici</v>
+        <v>Moviola Utd</v>
       </c>
       <c r="D18">
         <f>IF($A18="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A18),ScorerData!$E$2:$E$158,0)))</f>
@@ -47815,7 +47810,7 @@
       </c>
       <c r="B19" t="str">
         <f>IF($A19="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A19),ScorerData!$E$2:$E$158,0)))</f>
-        <v>FILIPPO ZANINI</v>
+        <v>GIANLUCA PAVAN</v>
       </c>
       <c r="C19" t="str">
         <f>IF($A19="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A19),ScorerData!$E$2:$E$158,0)))</f>
@@ -47833,11 +47828,11 @@
       </c>
       <c r="B20" t="str">
         <f>IF($A20="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A20),ScorerData!$E$2:$E$158,0)))</f>
-        <v>DANIEL TARGA</v>
+        <v>ELIA NAGLIERI</v>
       </c>
       <c r="C20" t="str">
         <f>IF($A20="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A20),ScorerData!$E$2:$E$158,0)))</f>
-        <v>Totani</v>
+        <v>Astolfi Impianti Elettrici</v>
       </c>
       <c r="D20">
         <f>IF($A20="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A20),ScorerData!$E$2:$E$158,0)))</f>
@@ -47851,11 +47846,11 @@
       </c>
       <c r="B21" t="str">
         <f>IF($A21="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A21),ScorerData!$E$2:$E$158,0)))</f>
-        <v>RICCARDO SANTARATO</v>
+        <v>FILIPPO ZANINI</v>
       </c>
       <c r="C21" t="str">
         <f>IF($A21="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A21),ScorerData!$E$2:$E$158,0)))</f>
-        <v>Totani</v>
+        <v>Astolfi Impianti Elettrici</v>
       </c>
       <c r="D21">
         <f>IF($A21="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A21),ScorerData!$E$2:$E$158,0)))</f>
@@ -47869,11 +47864,11 @@
       </c>
       <c r="B22" t="str">
         <f>IF($A22="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A22),ScorerData!$E$2:$E$158,0)))</f>
-        <v>LEONARDO FUSCO</v>
+        <v>DANIEL TARGA</v>
       </c>
       <c r="C22" t="str">
         <f>IF($A22="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A22),ScorerData!$E$2:$E$158,0)))</f>
-        <v>Vecchie Glorie Rovigo</v>
+        <v>Totani</v>
       </c>
       <c r="D22">
         <f>IF($A22="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A22),ScorerData!$E$2:$E$158,0)))</f>
@@ -47887,11 +47882,11 @@
       </c>
       <c r="B23" t="str">
         <f>IF($A23="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A23),ScorerData!$E$2:$E$158,0)))</f>
-        <v>NICOLÒ MARANGONI</v>
+        <v>RICCARDO SANTARATO</v>
       </c>
       <c r="C23" t="str">
         <f>IF($A23="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A23),ScorerData!$E$2:$E$158,0)))</f>
-        <v>AS Bancatore</v>
+        <v>Totani</v>
       </c>
       <c r="D23">
         <f>IF($A23="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A23),ScorerData!$E$2:$E$158,0)))</f>
@@ -47905,11 +47900,11 @@
       </c>
       <c r="B24" t="str">
         <f>IF($A24="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A24),ScorerData!$E$2:$E$158,0)))</f>
-        <v>MATTEO LONGO</v>
+        <v>LEONARDO FUSCO</v>
       </c>
       <c r="C24" t="str">
         <f>IF($A24="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A24),ScorerData!$E$2:$E$158,0)))</f>
-        <v>AS Bancatore</v>
+        <v>Vecchie Glorie Rovigo</v>
       </c>
       <c r="D24">
         <f>IF($A24="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A24),ScorerData!$E$2:$E$158,0)))</f>
@@ -47923,7 +47918,7 @@
       </c>
       <c r="B25" t="str">
         <f>IF($A25="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A25),ScorerData!$E$2:$E$158,0)))</f>
-        <v>GIANLUCA FREZZATI</v>
+        <v>NICOLÒ MARANGONI</v>
       </c>
       <c r="C25" t="str">
         <f>IF($A25="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A25),ScorerData!$E$2:$E$158,0)))</f>
@@ -47941,7 +47936,7 @@
       </c>
       <c r="B26" t="str">
         <f>IF($A26="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A26),ScorerData!$E$2:$E$158,0)))</f>
-        <v>NICOLA BARONI</v>
+        <v>MATTEO LONGO</v>
       </c>
       <c r="C26" t="str">
         <f>IF($A26="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A26),ScorerData!$E$2:$E$158,0)))</f>
@@ -47959,11 +47954,11 @@
       </c>
       <c r="B27" t="str">
         <f>IF($A27="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A27),ScorerData!$E$2:$E$158,0)))</f>
-        <v>LEONARDO MAGGIO</v>
+        <v>GIANLUCA FREZZATI</v>
       </c>
       <c r="C27" t="str">
         <f>IF($A27="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A27),ScorerData!$E$2:$E$158,0)))</f>
-        <v>Leoni di Ricky</v>
+        <v>AS Bancatore</v>
       </c>
       <c r="D27">
         <f>IF($A27="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A27),ScorerData!$E$2:$E$158,0)))</f>
@@ -47977,11 +47972,11 @@
       </c>
       <c r="B28" t="str">
         <f>IF($A28="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A28),ScorerData!$E$2:$E$158,0)))</f>
-        <v>TOMMASO FERRARESI</v>
+        <v>NICOLA BARONI</v>
       </c>
       <c r="C28" t="str">
         <f>IF($A28="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A28),ScorerData!$E$2:$E$158,0)))</f>
-        <v>Pink 5ive</v>
+        <v>AS Bancatore</v>
       </c>
       <c r="D28">
         <f>IF($A28="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A28),ScorerData!$E$2:$E$158,0)))</f>
@@ -47995,11 +47990,11 @@
       </c>
       <c r="B29" t="str">
         <f>IF($A29="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A29),ScorerData!$E$2:$E$158,0)))</f>
-        <v>LEONARDO BEDENDO</v>
+        <v>LEONARDO MAGGIO</v>
       </c>
       <c r="C29" t="str">
         <f>IF($A29="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A29),ScorerData!$E$2:$E$158,0)))</f>
-        <v>Pink 5ive</v>
+        <v>Leoni di Ricky</v>
       </c>
       <c r="D29">
         <f>IF($A29="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A29),ScorerData!$E$2:$E$158,0)))</f>
@@ -48013,11 +48008,11 @@
       </c>
       <c r="B30" t="str">
         <f>IF($A30="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A30),ScorerData!$E$2:$E$158,0)))</f>
-        <v>FRANCESCO BERARDI</v>
+        <v>TOMMASO FERRARESI</v>
       </c>
       <c r="C30" t="str">
         <f>IF($A30="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A30),ScorerData!$E$2:$E$158,0)))</f>
-        <v>Barrio Boys</v>
+        <v>Pink 5ive</v>
       </c>
       <c r="D30">
         <f>IF($A30="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A30),ScorerData!$E$2:$E$158,0)))</f>
@@ -48031,11 +48026,11 @@
       </c>
       <c r="B31" t="str">
         <f>IF($A31="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A31),ScorerData!$E$2:$E$158,0)))</f>
-        <v>FRANCESCO MARANGON</v>
+        <v>LEONARDO BEDENDO</v>
       </c>
       <c r="C31" t="str">
         <f>IF($A31="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A31),ScorerData!$E$2:$E$158,0)))</f>
-        <v>Barrio Boys</v>
+        <v>Pink 5ive</v>
       </c>
       <c r="D31">
         <f>IF($A31="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A31),ScorerData!$E$2:$E$158,0)))</f>
@@ -48049,11 +48044,11 @@
       </c>
       <c r="B32" t="str">
         <f>IF($A32="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A32),ScorerData!$E$2:$E$158,0)))</f>
-        <v>MARTINO GRANFO</v>
+        <v>FRANCESCO BERARDI</v>
       </c>
       <c r="C32" t="str">
         <f>IF($A32="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A32),ScorerData!$E$2:$E$158,0)))</f>
-        <v>All Blacks</v>
+        <v>Barrio Boys</v>
       </c>
       <c r="D32">
         <f>IF($A32="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A32),ScorerData!$E$2:$E$158,0)))</f>
@@ -48067,11 +48062,11 @@
       </c>
       <c r="B33" t="str">
         <f>IF($A33="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A33),ScorerData!$E$2:$E$158,0)))</f>
-        <v>STEFANO BRAGHIN</v>
+        <v>FRANCESCO MARANGON</v>
       </c>
       <c r="C33" t="str">
         <f>IF($A33="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A33),ScorerData!$E$2:$E$158,0)))</f>
-        <v>All Blacks</v>
+        <v>Barrio Boys</v>
       </c>
       <c r="D33">
         <f>IF($A33="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A33),ScorerData!$E$2:$E$158,0)))</f>
@@ -48085,7 +48080,7 @@
       </c>
       <c r="B34" t="str">
         <f>IF($A34="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A34),ScorerData!$E$2:$E$158,0)))</f>
-        <v>NICOLA BRESCIANI</v>
+        <v>MARTINO GRANFO</v>
       </c>
       <c r="C34" t="str">
         <f>IF($A34="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A34),ScorerData!$E$2:$E$158,0)))</f>
@@ -48103,7 +48098,7 @@
       </c>
       <c r="B35" t="str">
         <f>IF($A35="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A35),ScorerData!$E$2:$E$158,0)))</f>
-        <v>DAVIDE BEDESCHI</v>
+        <v>STEFANO BRAGHIN</v>
       </c>
       <c r="C35" t="str">
         <f>IF($A35="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A35),ScorerData!$E$2:$E$158,0)))</f>
@@ -48121,11 +48116,11 @@
       </c>
       <c r="B36" t="str">
         <f>IF($A36="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A36),ScorerData!$E$2:$E$158,0)))</f>
-        <v>ANGELO REDI</v>
+        <v>NICOLA BRESCIANI</v>
       </c>
       <c r="C36" t="str">
         <f>IF($A36="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A36),ScorerData!$E$2:$E$158,0)))</f>
-        <v>Boldò Glimt</v>
+        <v>All Blacks</v>
       </c>
       <c r="D36">
         <f>IF($A36="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A36),ScorerData!$E$2:$E$158,0)))</f>
@@ -48139,11 +48134,11 @@
       </c>
       <c r="B37" t="str">
         <f>IF($A37="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A37),ScorerData!$E$2:$E$158,0)))</f>
-        <v>ANDREA PAVAN</v>
+        <v>DAVIDE BEDESCHI</v>
       </c>
       <c r="C37" t="str">
         <f>IF($A37="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A37),ScorerData!$E$2:$E$158,0)))</f>
-        <v>Coca Juniors</v>
+        <v>All Blacks</v>
       </c>
       <c r="D37">
         <f>IF($A37="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A37),ScorerData!$E$2:$E$158,0)))</f>
@@ -48157,11 +48152,11 @@
       </c>
       <c r="B38" t="str">
         <f>IF($A38="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A38),ScorerData!$E$2:$E$158,0)))</f>
-        <v>RAFFAELE GAROFALO</v>
+        <v>NICOLÒ BERGANTIN</v>
       </c>
       <c r="C38" t="str">
         <f>IF($A38="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A38),ScorerData!$E$2:$E$158,0)))</f>
-        <v>Piadineria la Salsiccia</v>
+        <v>All Blacks</v>
       </c>
       <c r="D38">
         <f>IF($A38="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A38),ScorerData!$E$2:$E$158,0)))</f>
@@ -48169,39 +48164,39 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" t="str">
+      <c r="A39">
         <f>IFERROR(IF(INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,38),ScorerData!$E$2:$E$158,0))&gt;0,38,""),"")</f>
-        <v/>
+        <v>38</v>
       </c>
       <c r="B39" t="str">
         <f>IF($A39="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A39),ScorerData!$E$2:$E$158,0)))</f>
-        <v/>
+        <v>ANDREA PAVAN</v>
       </c>
       <c r="C39" t="str">
         <f>IF($A39="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A39),ScorerData!$E$2:$E$158,0)))</f>
-        <v/>
-      </c>
-      <c r="D39" t="str">
+        <v>Coca Juniors</v>
+      </c>
+      <c r="D39">
         <f>IF($A39="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A39),ScorerData!$E$2:$E$158,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" t="str">
+      <c r="A40">
         <f>IFERROR(IF(INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,39),ScorerData!$E$2:$E$158,0))&gt;0,39,""),"")</f>
-        <v/>
+        <v>39</v>
       </c>
       <c r="B40" t="str">
         <f>IF($A40="","",INDEX(ScorerData!$A$2:$A$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A40),ScorerData!$E$2:$E$158,0)))</f>
-        <v/>
+        <v>RAFFAELE GAROFALO</v>
       </c>
       <c r="C40" t="str">
         <f>IF($A40="","",INDEX(ScorerData!$B$2:$B$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A40),ScorerData!$E$2:$E$158,0)))</f>
-        <v/>
-      </c>
-      <c r="D40" t="str">
+        <v>Piadineria la Salsiccia</v>
+      </c>
+      <c r="D40">
         <f>IF($A40="","",INDEX(ScorerData!$D$2:$D$158,MATCH(LARGE(ScorerData!$E$2:$E$158,$A40),ScorerData!$E$2:$E$158,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -48422,40 +48417,40 @@
         <v>30</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="H1" s="5" t="s">
+        <v>575</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>578</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>579</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>580</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>581</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>582</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>583</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>584</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>587</v>
-      </c>
       <c r="M1" s="5" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
@@ -49107,7 +49102,7 @@
       </c>
       <c r="D14">
         <f>COUNTIFS(Matches!$G$2:$G$25,$B14,Matches!$L$2:$L$25,"Complete",Matches!$M$2:$M$25,3)+COUNTIFS(Matches!$H$2:$H$25,$B14,Matches!$L$2:$L$25,"Complete",Matches!$N$2:$N$25,3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <f>COUNTIFS(Matches!$G$2:$G$25,$B14,Matches!$L$2:$L$25,"Complete",Matches!$M$2:$M$25,2)+COUNTIFS(Matches!$H$2:$H$25,$B14,Matches!$L$2:$L$25,"Complete",Matches!$N$2:$N$25,2)</f>
@@ -49115,7 +49110,7 @@
       </c>
       <c r="F14">
         <f>COUNTIFS(Matches!$G$2:$G$25,$B14,Matches!$L$2:$L$25,"Complete",Matches!$M$2:$M$25,1)+COUNTIFS(Matches!$H$2:$H$25,$B14,Matches!$L$2:$L$25,"Complete",Matches!$N$2:$N$25,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14">
         <f>COUNTIFS(Matches!$G$2:$G$25,$B14,Matches!$L$2:$L$25,"Complete",Matches!$M$2:$M$25,0)+COUNTIFS(Matches!$H$2:$H$25,$B14,Matches!$L$2:$L$25,"Complete",Matches!$N$2:$N$25,0)</f>
@@ -49123,19 +49118,19 @@
       </c>
       <c r="H14">
         <f>SUMIFS(Matches!$I$2:$I$25,Matches!$G$2:$G$25,$B14,Matches!$L$2:$L$25,"Complete")+SUMIFS(Matches!$J$2:$J$25,Matches!$H$2:$H$25,$B14,Matches!$L$2:$L$25,"Complete")</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <f>SUMIFS(Matches!$J$2:$J$25,Matches!$G$2:$G$25,$B14,Matches!$L$2:$L$25,"Complete")+SUMIFS(Matches!$I$2:$I$25,Matches!$H$2:$H$25,$B14,Matches!$L$2:$L$25,"Complete")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <f>SUMIFS(Matches!$M$2:$M$25,Matches!$G$2:$G$25,$B14,Matches!$L$2:$L$25,"Complete")+SUMIFS(Matches!$N$2:$N$25,Matches!$H$2:$H$25,$B14,Matches!$L$2:$L$25,"Complete")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L14" s="2">
         <f>0</f>
@@ -49143,7 +49138,7 @@
       </c>
       <c r="M14">
         <f t="shared" si="1"/>
-        <v>999903.98600000003</v>
+        <v>3000106.986</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.3">
@@ -49163,7 +49158,7 @@
       </c>
       <c r="E15">
         <f>COUNTIFS(Matches!$G$2:$G$25,$B15,Matches!$L$2:$L$25,"Complete",Matches!$M$2:$M$25,2)+COUNTIFS(Matches!$H$2:$H$25,$B15,Matches!$L$2:$L$25,"Complete",Matches!$N$2:$N$25,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <f>COUNTIFS(Matches!$G$2:$G$25,$B15,Matches!$L$2:$L$25,"Complete",Matches!$M$2:$M$25,1)+COUNTIFS(Matches!$H$2:$H$25,$B15,Matches!$L$2:$L$25,"Complete",Matches!$N$2:$N$25,1)</f>
@@ -49171,23 +49166,23 @@
       </c>
       <c r="G15">
         <f>COUNTIFS(Matches!$G$2:$G$25,$B15,Matches!$L$2:$L$25,"Complete",Matches!$M$2:$M$25,0)+COUNTIFS(Matches!$H$2:$H$25,$B15,Matches!$L$2:$L$25,"Complete",Matches!$N$2:$N$25,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
         <f>SUMIFS(Matches!$I$2:$I$25,Matches!$G$2:$G$25,$B15,Matches!$L$2:$L$25,"Complete")+SUMIFS(Matches!$J$2:$J$25,Matches!$H$2:$H$25,$B15,Matches!$L$2:$L$25,"Complete")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15">
         <f>SUMIFS(Matches!$J$2:$J$25,Matches!$G$2:$G$25,$B15,Matches!$L$2:$L$25,"Complete")+SUMIFS(Matches!$I$2:$I$25,Matches!$H$2:$H$25,$B15,Matches!$L$2:$L$25,"Complete")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="K15">
         <f>SUMIFS(Matches!$M$2:$M$25,Matches!$G$2:$G$25,$B15,Matches!$L$2:$L$25,"Complete")+SUMIFS(Matches!$N$2:$N$25,Matches!$H$2:$H$25,$B15,Matches!$L$2:$L$25,"Complete")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2">
         <f>0</f>
@@ -49195,7 +49190,7 @@
       </c>
       <c r="M15">
         <f t="shared" si="1"/>
-        <v>2000000.9850000001</v>
+        <v>-198.01499999999999</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.3">
